--- a/agriculture 45.xlsx
+++ b/agriculture 45.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
-  <si>
-    <t xml:space="preserve">State-wise Yield Statistics of Cashew in India(1962-2021)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -269,11 +266,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -289,14 +287,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -387,7 +377,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -395,11 +385,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -407,7 +397,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -428,273 +418,280 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P59"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" customFormat="false" ht="15.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="2" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B4" s="3" t="n">
+        <v>0.00339270568276984</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.722004771780993</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>-0.000892227803606094</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>-0.00399032744626826</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>-4.54942177612918</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>-49.3412664683383</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.00339270568276984</v>
+        <v>0.0848147645542197</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0.722004771780993</v>
+        <v>1.04195695928162</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>-0.000892227803606094</v>
+        <v>0.108852763254164</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>-0.00399032744626826</v>
+        <v>0.00558668135164364</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0</v>
+        <v>31.5553438901457</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>-4.54942177612918</v>
+        <v>3.18207795176593</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>-49.3412664683383</v>
+        <v>59.3120805369127</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.0848147645542197</v>
+        <v>11.162333480221</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.04195695928162</v>
+        <v>0.741614697454929</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>0.108852763254164</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>0.00558668135164364</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>31.5553438901457</v>
+        <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>3.18207795176593</v>
+        <v>6.38279017214258</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>59.3120805369127</v>
+        <v>-9.42601369141654</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>11.162333480221</v>
+        <v>-0.00304933829359255</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.741614697454929</v>
+        <v>-9.15022738680094</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0</v>
+        <v>-0.00399026375642597</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0</v>
+        <v>-11.1751337436145</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>6.38279017214258</v>
+        <v>-5.66662501561914</v>
       </c>
       <c r="N7" s="3" t="n">
-        <v>-9.42601369141654</v>
+        <v>4.88372093023255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>-0.00304933829359255</v>
+        <v>0.0213460189674608</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>-9.15022738680094</v>
+        <v>12.0071654584722</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0</v>
+        <v>-0.00089126559714714</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>-0.00399026375642597</v>
+        <v>-0.000399042298493413</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-11.1751337436145</v>
+        <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>-5.66662501561914</v>
+        <v>0.209726913482133</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>4.88372093023255</v>
+        <v>28.5476718403548</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.0213460189674608</v>
+        <v>0.00152439024390105</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>12.0071654584722</v>
+        <v>27.7939703750206</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>-0.00089126559714714</v>
+        <v>0</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>-0.000399042298493413</v>
+        <v>0.00199521945418724</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.209726913482133</v>
+        <v>2.66346492774057</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>28.5476718403548</v>
+        <v>21.7766278568348</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00152439024390105</v>
+        <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>27.7939703750206</v>
+        <v>-1.09125359657536</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>0.000891273540770676</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.00199521945418724</v>
+        <v>0</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>-0.361141615061522</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>2.66346492774057</v>
+        <v>14.0018454539602</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>21.7766278568348</v>
+        <v>21.8838526912182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3" t="n">
-        <v>-1.09125359657536</v>
-      </c>
-      <c r="G11" s="3" t="n">
-        <v>0.000891273540770676</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>-0.361141615061522</v>
-      </c>
-      <c r="M11" s="3" t="n">
-        <v>14.0018454539602</v>
-      </c>
-      <c r="N11" s="3" t="n">
-        <v>21.8838526912182</v>
-      </c>
+      <c r="B11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B12" s="3"/>
@@ -706,7 +703,7 @@
       <c r="N12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="3"/>
@@ -718,7 +715,7 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="3"/>
@@ -730,1019 +727,1015 @@
       <c r="N14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
+      <c r="B15" s="3" t="n">
+        <v>23.9659442724458</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>-16.8622987360983</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>-15.1909847634501</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>-29.3841815320042</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>-14.9047658654246</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>14.0769114459957</v>
+      </c>
       <c r="N15" s="3"/>
+      <c r="O15" s="3" t="n">
+        <v>-18.9689758931968</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>1.67440271093773</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>23.9659442724458</v>
+        <v>-24.2813616043555</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>-16.8622987360983</v>
+        <v>27.8237307472903</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-15.1909847634501</v>
+        <v>54.6860257888668</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-29.3841815320042</v>
+        <v>60.1238294249671</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-14.9047658654246</v>
+        <v>-31.2237317955234</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>14.0769114459957</v>
+        <v>76.6457541751348</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3" t="n">
-        <v>-18.9689758931968</v>
+        <v>71.124911966195</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>1.67440271093773</v>
+        <v>0.509732530457918</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-24.2813616043555</v>
+        <v>-18.2231970579019</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>27.8237307472903</v>
+        <v>36.5078656699766</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>54.6860257888668</v>
+        <v>-4.60760394429197</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>60.1238294249671</v>
+        <v>-3.33307555486815</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-31.2237317955234</v>
+        <v>-9.76811388237524</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>76.6457541751348</v>
+        <v>-5.01975889150117</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3" t="n">
-        <v>71.124911966195</v>
+        <v>-16.8574778010576</v>
       </c>
       <c r="P17" s="3" t="n">
-        <v>0.509732530457918</v>
+        <v>9.27633962159</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>-18.2231970579019</v>
+        <v>-16.7362413535806</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>36.5078656699766</v>
+        <v>-34.2389172224402</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>-4.60760394429197</v>
+        <v>-25.9952932818258</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>-3.33307555486815</v>
+        <v>-42.029</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-9.76811388237524</v>
+        <v>8.77017981362385</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>-5.01975889150117</v>
+        <v>-1.8643844634628</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3" t="n">
-        <v>-16.8574778010576</v>
+        <v>0</v>
       </c>
       <c r="P18" s="3" t="n">
-        <v>9.27633962159</v>
+        <v>22.5953692370461</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>-16.7362413535806</v>
+        <v>91.8426661499709</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>-34.2389172224402</v>
+        <v>11.7176236639324</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>-25.9952932818258</v>
+        <v>27.8689114756459</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>-42.029</v>
+        <v>23.2150558037639</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>8.77017981362385</v>
+        <v>5.84998551983782</v>
       </c>
       <c r="M19" s="3" t="n">
-        <v>-1.8643844634628</v>
+        <v>13.1537284997451</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3" t="n">
-        <v>0</v>
+        <v>33.3328333358333</v>
       </c>
       <c r="P19" s="3" t="n">
-        <v>22.5953692370461</v>
+        <v>-21.5092455852071</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>91.8426661499709</v>
+        <v>22.5722149277851</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>11.7176236639324</v>
+        <v>46.7025631897473</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>27.8689114756459</v>
+        <v>-23.0768508873185</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>23.2150558037639</v>
+        <v>44.6275322348066</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.84998551983782</v>
+        <v>8.5704514363885</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>13.1537284997451</v>
+        <v>25.5448315112998</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3" t="n">
-        <v>33.3328333358333</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>-21.5092455852071</v>
+        <v>47.2228111087556</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
+      <c r="A21" s="2" t="s">
         <v>35</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>22.5722149277851</v>
+        <v>-40.5770082503322</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>46.7025631897473</v>
+        <v>-29.9996966663633</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>-23.0768508873185</v>
+        <v>-7.2797589273732</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>44.6275322348066</v>
+        <v>-21.5999070721933</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>8.5704514363885</v>
+        <v>37.6677376677377</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>25.5448315112998</v>
+        <v>29.5876541810695</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3" t="n">
-        <v>0</v>
+        <v>-15.6251054686182</v>
       </c>
       <c r="P21" s="3" t="n">
-        <v>47.2228111087556</v>
+        <v>-18.1816545467636</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
+      <c r="A22" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>-40.5770082503322</v>
+        <v>10.4208555778964</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>-29.9996966663633</v>
+        <v>-3.70498765004117</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>-7.2797589273732</v>
+        <v>14.4736842105263</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>-21.5999070721933</v>
+        <v>-11.0677597787436</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>37.6677376677377</v>
+        <v>-18.1829275733724</v>
       </c>
       <c r="M22" s="3" t="n">
-        <v>29.5876541810695</v>
+        <v>-25.4995991545806</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3" t="n">
-        <v>-15.6251054686182</v>
+        <v>3.704</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>-18.1816545467636</v>
+        <v>19.9978000219998</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>10.4208555778964</v>
+        <v>3.88044706768806</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>-3.70498765004117</v>
+        <v>-2.17352173521735</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>14.4736842105263</v>
+        <v>3.44827586206897</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>-11.0677597787436</v>
+        <v>3.18764924751487</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-18.1829275733724</v>
+        <v>8.75717801476621</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>-25.4995991545806</v>
+        <v>6.33327463755355</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3" t="n">
-        <v>3.704</v>
+        <v>14.2855306127697</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>19.9978000219998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>3.88044706768806</v>
+        <v>5.55639506769825</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>-2.17352173521735</v>
+        <v>12.5534753208519</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3.44827586206897</v>
+        <v>4.51000000000001</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>3.18764924751487</v>
+        <v>9.09127603465905</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>8.75717801476621</v>
+        <v>-1.84286767352956</v>
       </c>
       <c r="M24" s="3" t="n">
-        <v>6.33327463755355</v>
+        <v>-1.22175609038051</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3" t="n">
-        <v>14.2855306127697</v>
+        <v>12.4998593751758</v>
       </c>
       <c r="P24" s="3" t="n">
-        <v>0</v>
+        <v>6.66788889907417</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>5.55639506769825</v>
+        <v>-16.0136286201022</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>12.5534753208519</v>
+        <v>-7.50572175903221</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>4.51000000000001</v>
+        <v>-33.2918699964916</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>9.09127603465905</v>
+        <v>34.1251341251341</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-1.84286767352956</v>
+        <v>2.5708197981068</v>
       </c>
       <c r="M25" s="3" t="n">
-        <v>-1.22175609038051</v>
+        <v>-5.97570970866553</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3" t="n">
-        <v>12.4998593751758</v>
+        <v>-11.111</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>6.66788889907417</v>
+        <v>-18.7497851569214</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-16.0136286201022</v>
+        <v>-7.75393321628854</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-7.50572175903221</v>
+        <v>-0.581048538541418</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-33.2918699964916</v>
+        <v>33.4767710574548</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>34.1251341251341</v>
+        <v>5.17241379310345</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>2.5708197981068</v>
+        <v>10.6759747999319</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-5.97570970866553</v>
+        <v>-8.31088041841667</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3" t="n">
-        <v>-11.111</v>
+        <v>12.4998593751758</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>-18.7497851569214</v>
+        <v>3.84574704376706</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
+      <c r="A27" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.75393321628854</v>
+        <v>6.97919361395472</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.581048538541418</v>
+        <v>13.2888888888889</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>33.4767710574548</v>
+        <v>7.46268656716418</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.17241379310345</v>
+        <v>5.02469945355191</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>10.6759747999319</v>
+        <v>3.38461538461539</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-8.31088041841667</v>
+        <v>5.39962403578143</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3" t="n">
-        <v>12.4998593751758</v>
+        <v>0</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.84574704376706</v>
+        <v>7.40665295064267</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
+      <c r="A28" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>6.97919361395472</v>
+        <v>8.08014509024959</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>13.2888888888889</v>
+        <v>6.64770498234604</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>7.46268656716418</v>
+        <v>3.17444444444446</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>5.02469945355191</v>
+        <v>4.68440418907443</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>3.38461538461539</v>
+        <v>2.23511904761904</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>5.39962403578143</v>
+        <v>8.33538335383355</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>7.40665295064267</v>
+        <v>6.89779429893602</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
+      <c r="A29" s="2" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>8.08014509024959</v>
+        <v>-1.65406804851933</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0</v>
+        <v>-33.333</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>6.64770498234604</v>
+        <v>3.13781750629953</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>3.17444444444446</v>
+        <v>15.3849467460719</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>4.68440418907443</v>
+        <v>5.25173162410835</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>2.23511904761904</v>
+        <v>0.933015050507979</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8.33538335383355</v>
+        <v>-1.77496877720168</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.89779429893602</v>
+        <v>-3.22723724363068</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
+      <c r="A30" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-1.65406804851933</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>-33.333</v>
-      </c>
+        <v>-12.0900906756801</v>
+      </c>
+      <c r="D30" s="3"/>
       <c r="F30" s="3" t="n">
-        <v>3.13781750629953</v>
+        <v>-19.9019170753455</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>15.3849467460719</v>
+        <v>-14.4442474076701</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>5.25173162410835</v>
+        <v>-14.5142157714596</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.933015050507979</v>
+        <v>-15.289214484519</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-1.77496877720168</v>
+        <v>-13.0904677506357</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3" t="n">
-        <v>0</v>
+        <v>-9.09099999999999</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-3.22723724363068</v>
+        <v>-13.3321111009258</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
+      <c r="A31" s="2" t="s">
         <v>45</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-12.0900906756801</v>
+        <v>8.08162963510666</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>11.7655051926623</v>
       </c>
       <c r="D31" s="3"/>
       <c r="F31" s="3" t="n">
-        <v>-19.9019170753455</v>
+        <v>6.64366024713348</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-14.4442474076701</v>
+        <v>-0.699270184472056</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-14.5142157714596</v>
+        <v>1.56792731322308</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>-15.289214484519</v>
+        <v>3.97167225617543</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>-13.0904677506357</v>
+        <v>6.72755081683771</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3" t="n">
-        <v>-9.09099999999999</v>
+        <v>10.00011000011</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>-13.3321111009258</v>
+        <v>-9.34148456835826</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
+      <c r="A32" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>8.08162963510666</v>
+        <v>5.59090131691464</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>11.7655051926623</v>
-      </c>
-      <c r="D32" s="3"/>
+        <v>92.9814506044185</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.438666666666654</v>
+      </c>
       <c r="F32" s="3" t="n">
-        <v>6.64366024713348</v>
+        <v>13.5952733877534</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>-0.699270184472056</v>
+        <v>-1.93571067607058</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>1.56792731322308</v>
+        <v>2.71152222908706</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>3.97167225617543</v>
+        <v>-0.199757671022038</v>
       </c>
       <c r="M32" s="3" t="n">
-        <v>6.72755081683771</v>
+        <v>-8.64002658469719</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3" t="n">
-        <v>10.00011000011</v>
+        <v>5.45499999999999</v>
       </c>
       <c r="P32" s="3" t="n">
-        <v>-9.34148456835826</v>
+        <v>16.8700562335208</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
+      <c r="A33" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>5.59090131691464</v>
+        <v>3.96183935599865</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>92.9814506044185</v>
+        <v>-36.000036000036</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.438666666666654</v>
+        <v>1.63748357206388</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>5.0006562541016</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>13.5952733877534</v>
+        <v>12.2879564793884</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>-1.93571067607058</v>
+        <v>1.60310987632193</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>2.71152222908706</v>
+        <v>3.30416070082096</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>-1.69955555555554</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>-0.199757671022038</v>
+        <v>0.900708754429713</v>
       </c>
       <c r="M33" s="3" t="n">
-        <v>-8.64002658469719</v>
-      </c>
-      <c r="N33" s="3"/>
+        <v>4.00109120669274</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>-18.7142796363791</v>
+      </c>
       <c r="O33" s="3" t="n">
-        <v>5.45499999999999</v>
+        <v>4.3098952159689</v>
       </c>
       <c r="P33" s="3" t="n">
-        <v>16.8700562335208</v>
+        <v>4.16674985525187</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
+      <c r="A34" s="2" t="s">
         <v>48</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>3.96183935599865</v>
+        <v>-15.4475344706707</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>-36.000036000036</v>
+        <v>-9.00704532350832</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.63748357206388</v>
+        <v>0</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>5.0006562541016</v>
+        <v>-16.6675</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>12.2879564793884</v>
+        <v>6.30309180483493</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1.60310987632193</v>
+        <v>4.02558024146866</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>3.30416070082096</v>
+        <v>5.1643115481453</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>-1.69955555555554</v>
+        <v>-50</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.900708754429713</v>
+        <v>-16.5086746556967</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>4.00109120669274</v>
+        <v>5.68768033575238</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>-18.7142796363791</v>
+        <v>-41.8436066088595</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>4.3098952159689</v>
+        <v>5.51909090909091</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>4.16674985525187</v>
+        <v>7.0686548855752</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
+      <c r="A35" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>-15.4475344706707</v>
+        <v>-0.63939561452</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>-9.00704532350832</v>
+        <v>-4.11399252001359</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0</v>
+        <v>7.38285714285714</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>-16.6675</v>
+        <v>-8.96708967089671</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>6.30309180483493</v>
+        <v>-0.61279793065222</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>4.02558024146866</v>
+        <v>0.312678862908866</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>5.1643115481453</v>
+        <v>-1.57685409030648</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>-89.99982000036</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>-50</v>
+        <v>-4.25543458603105</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-16.5086746556967</v>
+        <v>-7.70429228012776</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>5.68768033575238</v>
+        <v>-1.31540847983455</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>-41.8436066088595</v>
+        <v>-11.7644411777941</v>
       </c>
       <c r="O35" s="3" t="n">
-        <v>5.51909090909091</v>
-      </c>
-      <c r="P35" s="3" t="n">
-        <v>7.0686548855752</v>
-      </c>
+        <v>-1.40775904403341</v>
+      </c>
+      <c r="P35" s="3"/>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="0" t="s">
+      <c r="A36" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>-0.63939561452</v>
+        <v>-4.56206071620645</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>-4.11399252001359</v>
+        <v>-5.88292179743408</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>7.38285714285714</v>
+        <v>-72.6242169920331</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>-8.96708967089671</v>
+        <v>11.1092802530978</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>-0.61279793065222</v>
+        <v>-10.1456235476375</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.312678862908866</v>
+        <v>-12.5653786413922</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>-1.57685409030648</v>
+        <v>-6.3823212474645</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>-89.99982000036</v>
+        <v>113.331733365333</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>-4.25543458603105</v>
+        <v>11.1123703745679</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>170</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-7.70429228012776</v>
+        <v>-7.13411546252533</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>-1.31540847983455</v>
+        <v>-13.989604728172</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>-11.7644411777941</v>
+        <v>19.9986400108799</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>-1.40775904403341</v>
+        <v>-7.69244212973077</v>
       </c>
       <c r="P36" s="3"/>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="0" t="s">
+      <c r="A37" s="2" t="s">
         <v>51</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>-4.56206071620645</v>
+        <v>16.6391387987486</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>-5.88292179743408</v>
+        <v>16.6249957187382</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-72.6242169920331</v>
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>11.1092802530978</v>
+        <v>16.6009194720451</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>-10.1456235476375</v>
+        <v>14.8152618058309</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>-12.5653786413922</v>
+        <v>11.6895672455256</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>-6.3823212474645</v>
+        <v>16.6402884395657</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>113.331733365333</v>
+        <v>1.24873439082012</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>11.1123703745679</v>
+        <v>16.5986672106623</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-7.13411546252533</v>
+        <v>16.3777237508805</v>
       </c>
       <c r="M37" s="3" t="n">
-        <v>-13.989604728172</v>
+        <v>16.4307122493238</v>
       </c>
       <c r="N37" s="3" t="n">
-        <v>19.9986400108799</v>
+        <v>14.9997166657222</v>
       </c>
       <c r="O37" s="3" t="n">
-        <v>-7.69244212973077</v>
+        <v>8.00026506617188</v>
       </c>
       <c r="P37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
+      <c r="A38" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>16.6391387987486</v>
+        <v>4.27981208143138</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>16.6249957187382</v>
+        <v>5.3596076473525</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>0</v>
+        <v>-0.414315546274491</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>16.6009194720451</v>
+        <v>5.14601139601141</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>14.8152618058309</v>
+        <v>4.06943568489653</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>11.6895672455256</v>
+        <v>2.798035099868</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>16.6402884395657</v>
+        <v>2.12024903130306</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>1.24873439082012</v>
+        <v>0</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>16.5986672106623</v>
+        <v>3.99632588791041</v>
       </c>
       <c r="K38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>16.3777237508805</v>
+        <v>-0.779007790077912</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>16.4307122493238</v>
+        <v>4.48285965426312</v>
       </c>
       <c r="N38" s="3" t="n">
-        <v>14.9997166657222</v>
+        <v>0</v>
       </c>
       <c r="O38" s="3" t="n">
-        <v>8.00026506617188</v>
+        <v>0</v>
       </c>
       <c r="P38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
+      <c r="A39" s="2" t="s">
         <v>53</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>4.27981208143138</v>
+        <v>-8.20672577681924</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>5.3596076473525</v>
+        <v>-2.72187534842234</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-0.414315546274491</v>
+        <v>-14.6204896547878</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>5.14601139601141</v>
+        <v>-10.5286077174308</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>4.06943568489653</v>
+        <v>-6.64896687059909</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2.798035099868</v>
+        <v>-9.73181205793197</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>2.12024903130306</v>
+        <v>-19.9671725784447</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0</v>
+        <v>-5.86388888888889</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>3.99632588791041</v>
+        <v>-8.13834485272469</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0</v>
+        <v>-5.92592592592592</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>-0.779007790077912</v>
+        <v>-11.2121212121212</v>
       </c>
       <c r="M39" s="3" t="n">
-        <v>4.48285965426312</v>
+        <v>-8.3667174104639</v>
       </c>
       <c r="N39" s="3" t="n">
-        <v>0</v>
+        <v>-5.99931014092836</v>
       </c>
       <c r="O39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" s="3"/>
+        <v>-6.0034185037472</v>
+      </c>
+      <c r="P39" s="3" t="n">
+        <v>-6.16349848675486</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
+      <c r="A40" s="2" t="s">
         <v>54</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>-8.20672577681924</v>
+        <v>4.38755264715094</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>-2.72187534842234</v>
+        <v>-10.6305247926188</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-14.6204896547878</v>
+        <v>-8.4026807059715</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-10.5286077174308</v>
+        <v>0.529973230943948</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>-6.64896687059909</v>
+        <v>-17.571410906393</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>-9.73181205793197</v>
+        <v>-17.8598913271612</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>-19.9671725784447</v>
+        <v>-16.0394193634305</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>-5.86388888888889</v>
+        <v>-1.64065035852341</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>-8.13834485272469</v>
+        <v>64.7564251266711</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>-5.92592592592592</v>
+        <v>-1.5748031496063</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-11.2121212121212</v>
+        <v>13.9178227915429</v>
       </c>
       <c r="M40" s="3" t="n">
-        <v>-8.3667174104639</v>
+        <v>1.95204057096638</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>-5.99931014092836</v>
+        <v>-2.47293790789713</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>-6.0034185037472</v>
+        <v>-10.0199559849304</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>-6.16349848675486</v>
+        <v>-16.2278714961315</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
+      <c r="A41" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>4.38755264715094</v>
+        <v>2.99271411660749</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>-10.6305247926188</v>
+        <v>1.24881771108869</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>-8.4026807059715</v>
+        <v>-5.89888041075376</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.529973230943948</v>
+        <v>5.17496436160196</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>-17.571410906393</v>
+        <v>1.26575157515751</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>-17.8598913271612</v>
+        <v>0.550784299808371</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>-16.0394193634305</v>
+        <v>5.02490245217777</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>-1.64065035852341</v>
+        <v>0</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>64.7564251266711</v>
+        <v>5.2623778426196</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>-1.5748031496063</v>
+        <v>-66.667</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>13.9178227915429</v>
+        <v>4.99980545504066</v>
       </c>
       <c r="M41" s="3" t="n">
-        <v>1.95204057096638</v>
+        <v>-5.50600343053173</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>-2.47293790789713</v>
+        <v>6.2497480482135</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>-10.0199559849304</v>
+        <v>4.54550165300391</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>-16.2278714961315</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
+        <v>4.11610754223175</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B42" s="3" t="n">
-        <v>2.99271411660749</v>
-      </c>
-      <c r="C42" s="3" t="n">
-        <v>1.24881771108869</v>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>-5.89888041075376</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>5.17496436160196</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>1.26575157515751</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>0.550784299808371</v>
-      </c>
-      <c r="H42" s="3" t="n">
-        <v>5.02490245217777</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>5.2623778426196</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>-66.667</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>4.99980545504066</v>
-      </c>
-      <c r="M42" s="3" t="n">
-        <v>-5.50600343053173</v>
-      </c>
-      <c r="N42" s="3" t="n">
-        <v>6.2497480482135</v>
-      </c>
-      <c r="O42" s="3" t="n">
-        <v>4.54550165300391</v>
-      </c>
-      <c r="P42" s="3" t="n">
-        <v>4.11610754223175</v>
-      </c>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4" t="s">
+      <c r="A43" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="s">
@@ -1808,27 +1801,27 @@
       <c r="C52" s="6"/>
       <c r="D52" s="6"/>
     </row>
-    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+    <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="7"/>
+      <c r="B53" s="7"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+    </row>
+    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-    </row>
-    <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="7"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="7" t="s">
+      <c r="A55" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
@@ -1854,16 +1847,10 @@
       <c r="C58" s="6"/>
       <c r="D58" s="6"/>
     </row>
-    <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A43:D43"/>
     <mergeCell ref="A44:D44"/>
     <mergeCell ref="A45:D45"/>
@@ -1880,7 +1867,6 @@
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A57:D57"/>
     <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A59:D59"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
